--- a/analyses/data/raw_data/Gold_Standard_Overview_09022026.xlsx
+++ b/analyses/data/raw_data/Gold_Standard_Overview_09022026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://umcutrecht-my.sharepoint.com/personal/s_l_kampman-2_umcutrecht_nl/Documents/Documenten/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/skampma2/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{94B75DFC-BF97-4547-947C-47F4BC98F594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E61BC4A-E60E-9C4B-8FA9-9B060AE673B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17280" xr2:uid="{4E3F4CC3-0563-A146-9958-FFCF367891F9}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{4E3F4CC3-0563-A146-9958-FFCF367891F9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,74 +41,11 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={75AB4224-1F14-4597-AD70-98F6EC982131}</author>
-    <author>tc={329BDBA6-BB80-4B3D-95B0-D07D4B1FF506}</author>
-    <author>tc={D3E0D24D-848B-4B1C-BE9F-07B1DEA58E92}</author>
-    <author>tc={0A52EC41-B561-484D-94A7-3CEBCD03DE91}</author>
-    <author>tc={3A043531-3B6F-46A3-8F65-728DDF3FF3FB}</author>
-    <author>tc={67D8EDD5-9FE9-4AA3-9251-B11007B9DF44}</author>
-    <author>tc={AC2A43FB-321E-47C3-86B8-68B205EC39E4}</author>
     <author>tc={7BC7DBB5-BFD6-47AD-A1AA-C4EEFF1AC062}</author>
     <author>tc={86BAC9D1-E126-4F5D-8F7A-054BC788F1E2}</author>
   </authors>
   <commentList>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{75AB4224-1F14-4597-AD70-98F6EC982131}">
-      <text>
-        <t>[Opmerkingenthread]
-U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
-Opmerking:
-    Remove this column later</t>
-      </text>
-    </comment>
-    <comment ref="C123" authorId="1" shapeId="0" xr:uid="{329BDBA6-BB80-4B3D-95B0-D07D4B1FF506}">
-      <text>
-        <t>[Opmerkingenthread]
-U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
-Opmerking:
-    Is dit Onicas 2023?</t>
-      </text>
-    </comment>
-    <comment ref="C128" authorId="2" shapeId="0" xr:uid="{D3E0D24D-848B-4B1C-BE9F-07B1DEA58E92}">
-      <text>
-        <t>[Opmerkingenthread]
-U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
-Opmerking:
-    Is dit meier 2017?</t>
-      </text>
-    </comment>
-    <comment ref="C150" authorId="3" shapeId="0" xr:uid="{0A52EC41-B561-484D-94A7-3CEBCD03DE91}">
-      <text>
-        <t>[Opmerkingenthread]
-U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
-Opmerking:
-    Churchill 2019B</t>
-      </text>
-    </comment>
-    <comment ref="C151" authorId="4" shapeId="0" xr:uid="{3A043531-3B6F-46A3-8F65-728DDF3FF3FB}">
-      <text>
-        <t>[Opmerkingenthread]
-U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
-Opmerking:
-    Churchill 2019A</t>
-      </text>
-    </comment>
-    <comment ref="C183" authorId="5" shapeId="0" xr:uid="{67D8EDD5-9FE9-4AA3-9251-B11007B9DF44}">
-      <text>
-        <t>[Opmerkingenthread]
-U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
-Opmerking:
-    Should this not be Deb? ?</t>
-      </text>
-    </comment>
-    <comment ref="C187" authorId="6" shapeId="0" xr:uid="{AC2A43FB-321E-47C3-86B8-68B205EC39E4}">
-      <text>
-        <t>[Opmerkingenthread]
-U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
-Opmerking:
-    Asselstine_2020</t>
-      </text>
-    </comment>
-    <comment ref="C249" authorId="7" shapeId="0" xr:uid="{7BC7DBB5-BFD6-47AD-A1AA-C4EEFF1AC062}">
+    <comment ref="C249" authorId="0" shapeId="0" xr:uid="{7BC7DBB5-BFD6-47AD-A1AA-C4EEFF1AC062}">
       <text>
         <t>[Opmerkingenthread]
 U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
@@ -116,7 +53,7 @@
     Frohlich 2021B</t>
       </text>
     </comment>
-    <comment ref="C250" authorId="8" shapeId="0" xr:uid="{86BAC9D1-E126-4F5D-8F7A-054BC788F1E2}">
+    <comment ref="C250" authorId="1" shapeId="0" xr:uid="{86BAC9D1-E126-4F5D-8F7A-054BC788F1E2}">
       <text>
         <t>[Opmerkingenthread]
 U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1501,27 +1438,6 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="C1" dT="2026-02-23T08:33:52.20" personId="{BCF090F6-C932-4165-B66C-F759561C7FAF}" id="{75AB4224-1F14-4597-AD70-98F6EC982131}">
-    <text>Remove this column later</text>
-  </threadedComment>
-  <threadedComment ref="C123" dT="2026-02-23T09:41:07.72" personId="{BCF090F6-C932-4165-B66C-F759561C7FAF}" id="{329BDBA6-BB80-4B3D-95B0-D07D4B1FF506}">
-    <text>Is dit Onicas 2023?</text>
-  </threadedComment>
-  <threadedComment ref="C128" dT="2026-02-23T09:20:57.91" personId="{BCF090F6-C932-4165-B66C-F759561C7FAF}" id="{D3E0D24D-848B-4B1C-BE9F-07B1DEA58E92}">
-    <text>Is dit meier 2017?</text>
-  </threadedComment>
-  <threadedComment ref="C150" dT="2026-02-23T09:24:48.25" personId="{BCF090F6-C932-4165-B66C-F759561C7FAF}" id="{0A52EC41-B561-484D-94A7-3CEBCD03DE91}">
-    <text>Churchill 2019B</text>
-  </threadedComment>
-  <threadedComment ref="C151" dT="2026-02-23T09:24:39.88" personId="{BCF090F6-C932-4165-B66C-F759561C7FAF}" id="{3A043531-3B6F-46A3-8F65-728DDF3FF3FB}">
-    <text>Churchill 2019A</text>
-  </threadedComment>
-  <threadedComment ref="C183" dT="2026-02-23T09:01:44.98" personId="{BCF090F6-C932-4165-B66C-F759561C7FAF}" id="{67D8EDD5-9FE9-4AA3-9251-B11007B9DF44}">
-    <text>Should this not be Deb? ?</text>
-  </threadedComment>
-  <threadedComment ref="C187" dT="2026-02-23T08:56:26.61" personId="{BCF090F6-C932-4165-B66C-F759561C7FAF}" id="{AC2A43FB-321E-47C3-86B8-68B205EC39E4}">
-    <text>Asselstine_2020</text>
-  </threadedComment>
   <threadedComment ref="C249" dT="2026-02-23T08:44:40.14" personId="{BCF090F6-C932-4165-B66C-F759561C7FAF}" id="{7BC7DBB5-BFD6-47AD-A1AA-C4EEFF1AC062}">
     <text>Frohlich 2021B</text>
   </threadedComment>
